--- a/templates_formats/Inscripcion.xlsx
+++ b/templates_formats/Inscripcion.xlsx
@@ -138,9 +138,6 @@
     <t>de:</t>
   </si>
   <si>
-    <t>, xxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxx</t>
-  </si>
-  <si>
     <t>, Representante Legal</t>
   </si>
   <si>
@@ -157,6 +154,9 @@
   </si>
   <si>
     <t>"NOMBRE MUNICIPIO","NOMBRE ESTADO"</t>
+  </si>
+  <si>
+    <t>, xxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxx</t>
   </si>
 </sst>
 </file>
@@ -188,7 +188,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -298,6 +298,41 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thick">
         <color indexed="64"/>
       </left>
@@ -307,16 +342,14 @@
       <top style="thick">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -354,80 +387,98 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="14"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="16"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="19"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="20"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="23"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="4"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="4"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="18"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -441,121 +492,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>732692</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>14654</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1011116</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>29308</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Rectangle 3"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4161692" y="6359769"/>
-          <a:ext cx="278424" cy="227135"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-ES" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>732692</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>211015</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1009650</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>13188</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="Rectangle 4"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4161692" y="6556130"/>
-          <a:ext cx="276958" cy="227135"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-ES" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -845,160 +781,189 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:T70"/>
+  <dimension ref="A1:V70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.75" customWidth="1"/>
-    <col min="2" max="2" width="3.875" customWidth="1"/>
+    <col min="2" max="2" width="2.75" customWidth="1"/>
     <col min="3" max="3" width="14.125" customWidth="1"/>
-    <col min="4" max="4" width="3.375" customWidth="1"/>
+    <col min="4" max="4" width="2.375" customWidth="1"/>
     <col min="5" max="5" width="9.875" customWidth="1"/>
-    <col min="6" max="6" width="5.5" customWidth="1"/>
-    <col min="7" max="7" width="6.5" customWidth="1"/>
-    <col min="8" max="8" width="13.625" customWidth="1"/>
-    <col min="9" max="9" width="16.25" customWidth="1"/>
-    <col min="10" max="10" width="11.75" customWidth="1"/>
-    <col min="11" max="11" width="2.875" customWidth="1"/>
-    <col min="12" max="12" width="11.875" customWidth="1"/>
-    <col min="13" max="13" width="12.125" customWidth="1"/>
-    <col min="14" max="14" width="12.625" customWidth="1"/>
-    <col min="15" max="15" width="3.875" customWidth="1"/>
-    <col min="16" max="16" width="9.625" customWidth="1"/>
-    <col min="17" max="17" width="10.25" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
-    <col min="21" max="21" width="9" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="2" customWidth="1"/>
+    <col min="8" max="8" width="5.5" customWidth="1"/>
+    <col min="9" max="9" width="11.875" customWidth="1"/>
+    <col min="10" max="10" width="2.75" customWidth="1"/>
+    <col min="11" max="11" width="12.875" customWidth="1"/>
+    <col min="12" max="12" width="11.75" customWidth="1"/>
+    <col min="13" max="13" width="2.875" customWidth="1"/>
+    <col min="14" max="14" width="11.875" customWidth="1"/>
+    <col min="15" max="15" width="12.125" customWidth="1"/>
+    <col min="16" max="16" width="12.625" customWidth="1"/>
+    <col min="17" max="17" width="3.875" customWidth="1"/>
+    <col min="18" max="18" width="9.625" customWidth="1"/>
+    <col min="19" max="19" width="10.25" customWidth="1"/>
+    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="23" max="23" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C1" s="19" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-    </row>
-    <row r="2" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C2" s="41" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="S2" s="1"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="Q2" s="1"/>
-    </row>
-    <row r="3" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C3" s="16" t="s">
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="O4" s="5"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-    </row>
-    <row r="4" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="M4" s="5"/>
-    </row>
-    <row r="5" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C5" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="M5" s="2"/>
-      <c r="O5" s="1"/>
-    </row>
-    <row r="6" spans="3:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="2"/>
-      <c r="O6" s="1"/>
-      <c r="R6" s="3"/>
-    </row>
-    <row r="7" spans="3:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="23" t="s">
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="47"/>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
+      <c r="O5" s="2"/>
+      <c r="Q5" s="1"/>
+    </row>
+    <row r="6" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="2"/>
+      <c r="Q6" s="1"/>
+      <c r="T6" s="3"/>
+    </row>
+    <row r="7" spans="1:21" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C7" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="26" t="s">
+      <c r="G7" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="27" t="s">
+      <c r="H7" s="46"/>
+      <c r="I7" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="27" t="s">
+      <c r="J7" s="26"/>
+      <c r="K7" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="J7" s="1"/>
-      <c r="M7" s="2"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="O7" s="2"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
-    </row>
-    <row r="8" spans="3:19" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="D8" s="25"/>
-      <c r="E8" s="30"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+    </row>
+    <row r="8" spans="1:21" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="27"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="31"/>
       <c r="F8" s="31"/>
       <c r="G8" s="32"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="38"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="35"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
-    </row>
-    <row r="9" spans="3:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="1"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="36"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+    </row>
+    <row r="9" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="27"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="18"/>
       <c r="I9" s="38"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="39"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -1006,63 +971,71 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
-    </row>
-    <row r="10" spans="3:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+    </row>
+    <row r="10" spans="1:21" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="1"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="36"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="18"/>
       <c r="I10" s="38"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="39"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
-    </row>
-    <row r="11" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D11" s="25"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="1"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+    </row>
+    <row r="11" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D11" s="19"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="1"/>
+      <c r="P11" s="6"/>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
-    </row>
-    <row r="12" spans="3:19" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+    </row>
+    <row r="12" spans="1:21" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D12" s="1"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="37"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="44"/>
+      <c r="P12" s="6"/>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
-    </row>
-    <row r="13" spans="3:19" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="N13" s="6"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+    </row>
+    <row r="13" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="P13" s="6"/>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
-    </row>
-    <row r="14" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C14" s="1" t="s">
         <v>1</v>
       </c>
@@ -1071,20 +1044,20 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
-      <c r="I14" s="5" t="s">
+      <c r="J14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
       <c r="L14" s="1"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="P14" s="6"/>
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
-    </row>
-    <row r="15" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
@@ -1093,18 +1066,18 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
-      <c r="I15" s="5" t="s">
+      <c r="J15" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="J15" s="1"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="P15" s="6"/>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
-    </row>
-    <row r="16" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
@@ -1113,18 +1086,18 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
+      <c r="J16" s="7"/>
       <c r="L16" s="1"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="P16" s="6"/>
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
-    </row>
-    <row r="17" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+    </row>
+    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
       <c r="C17" s="1" t="s">
         <v>4</v>
       </c>
@@ -1133,20 +1106,20 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
-      <c r="I17" s="7" t="s">
+      <c r="J17" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
       <c r="L17" s="1"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="P17" s="6"/>
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
-    </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+    </row>
+    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
       <c r="C18" s="1" t="s">
         <v>8</v>
       </c>
@@ -1155,20 +1128,20 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
-      <c r="I18" s="7" t="s">
+      <c r="J18" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
       <c r="L18" s="1"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="P18" s="6"/>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
-    </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+    </row>
+    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
       <c r="C19" s="1" t="s">
         <v>7</v>
       </c>
@@ -1177,46 +1150,47 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
+      <c r="J19" s="7"/>
       <c r="L19" s="1"/>
-      <c r="N19" s="6"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="P19" s="6"/>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
-    </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+    </row>
+    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
         <v>9</v>
       </c>
-      <c r="I20" s="7" t="s">
+      <c r="J20" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="N20" s="6"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="P20" s="6"/>
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
-    </row>
-    <row r="21" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+    </row>
+    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
         <v>13</v>
       </c>
       <c r="G21" s="1"/>
-      <c r="N21" s="6"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="P21" s="6"/>
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
-    </row>
-    <row r="22" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+    </row>
+    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -1225,57 +1199,59 @@
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="P22" s="7"/>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
-    </row>
-    <row r="23" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+    </row>
+    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
       <c r="C23" s="9" t="s">
         <v>14</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
-      <c r="H23" s="29" t="s">
+      <c r="I23" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="I23" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="M23" s="1"/>
-      <c r="N23" s="6"/>
+      <c r="K23" s="22" t="s">
+        <v>40</v>
+      </c>
       <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
+      <c r="P23" s="6"/>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
-    </row>
-    <row r="24" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+    </row>
+    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
       <c r="C24" s="8" t="s">
         <v>39</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
-      <c r="G24" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H24" s="1"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="6"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
+      <c r="I24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J24" s="1"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="6"/>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
-    </row>
-    <row r="25" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+    </row>
+    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
       <c r="C25" s="8" t="s">
         <v>21</v>
       </c>
@@ -1286,17 +1262,19 @@
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
       <c r="J25" s="8"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="6"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6"/>
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
-    </row>
-    <row r="26" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+    </row>
+    <row r="26" spans="2:21" x14ac:dyDescent="0.25">
       <c r="C26" s="8" t="s">
         <v>22</v>
       </c>
@@ -1307,18 +1285,22 @@
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
       <c r="J26" s="8"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="6"/>
-      <c r="N26" s="6"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="21"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="6"/>
+      <c r="P26" s="6"/>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
-    </row>
-    <row r="27" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="C27" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+    </row>
+    <row r="27" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="C27" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -1328,15 +1310,14 @@
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
-      <c r="M27" s="6"/>
-      <c r="Q27" s="1"/>
-      <c r="R27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="6"/>
       <c r="S27" s="1"/>
-    </row>
-    <row r="28" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="C28" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1"/>
+    </row>
+    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
@@ -1346,12 +1327,14 @@
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
-      <c r="M28" s="6"/>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="6"/>
       <c r="S28" s="1"/>
-    </row>
-    <row r="29" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+    </row>
+    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -1362,13 +1345,15 @@
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
-      <c r="M29" s="6"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="6"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
-    </row>
-    <row r="30" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T29" s="1"/>
+      <c r="U29" s="1"/>
+    </row>
+    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
       <c r="C30" s="8" t="s">
         <v>32</v>
       </c>
@@ -1376,137 +1361,145 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="40" t="s">
+      <c r="H30" s="1"/>
+      <c r="I30" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="M30" s="6"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
+      <c r="J30" s="24"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="O30" s="6"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
-    </row>
-    <row r="31" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T30" s="1"/>
+      <c r="U30" s="1"/>
+    </row>
+    <row r="31" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
-    </row>
-    <row r="32" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="22"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+    </row>
+    <row r="32" spans="2:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="17"/>
       <c r="C32" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D32" s="11"/>
       <c r="G32" s="1"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="10" t="s">
+      <c r="H32" s="1"/>
+      <c r="I32" s="23"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="K32" s="1"/>
-      <c r="M32" s="13"/>
-      <c r="O32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="O32" s="13"/>
       <c r="Q32" s="1"/>
-      <c r="R32" s="1"/>
       <c r="S32" s="1"/>
-    </row>
-    <row r="33" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="22"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+    </row>
+    <row r="33" spans="2:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="17"/>
       <c r="C33" s="11" t="s">
         <v>26</v>
       </c>
       <c r="D33" s="11"/>
       <c r="G33" s="1"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="10" t="s">
+      <c r="H33" s="1"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="K33" s="1"/>
-      <c r="N33" s="6"/>
-      <c r="O33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="P33" s="6"/>
       <c r="Q33" s="1"/>
-      <c r="R33" s="1"/>
       <c r="S33" s="1"/>
-    </row>
-    <row r="34" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="22"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+    </row>
+    <row r="34" spans="2:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="17"/>
       <c r="C34" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D34" s="11"/>
-      <c r="K34" s="1"/>
-      <c r="M34" s="6"/>
-      <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="O34" s="6"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
-    </row>
-    <row r="35" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="22"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+    </row>
+    <row r="35" spans="2:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="17"/>
       <c r="C35" s="11" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="11"/>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
-    </row>
-    <row r="36" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="22"/>
+      <c r="T35" s="1"/>
+      <c r="U35" s="1"/>
+    </row>
+    <row r="36" spans="2:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="17"/>
       <c r="C36" s="11" t="s">
         <v>27</v>
       </c>
       <c r="D36" s="11"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="1"/>
-      <c r="P36" s="1"/>
+      <c r="P36" s="6"/>
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
-    </row>
-    <row r="37" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="22"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="1"/>
+    </row>
+    <row r="37" spans="2:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="17"/>
       <c r="C37" s="11" t="s">
         <v>23</v>
       </c>
       <c r="D37" s="11"/>
-      <c r="M37" s="6"/>
-      <c r="N37" s="6"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
+      <c r="O37" s="6"/>
+      <c r="P37" s="6"/>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
-    </row>
-    <row r="38" spans="2:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="22"/>
+      <c r="T37" s="1"/>
+      <c r="U37" s="1"/>
+    </row>
+    <row r="38" spans="2:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="17"/>
       <c r="C38" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D38" s="11"/>
-      <c r="M38" s="6"/>
-      <c r="N38" s="6"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
+      <c r="O38" s="6"/>
+      <c r="P38" s="6"/>
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
-    </row>
-    <row r="39" spans="2:19" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="M39" s="6"/>
-      <c r="O39" s="1"/>
-      <c r="P39" s="1"/>
+      <c r="T38" s="1"/>
+      <c r="U38" s="1"/>
+    </row>
+    <row r="39" spans="2:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="O39" s="6"/>
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T39" s="1"/>
+      <c r="U39" s="1"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.25">
       <c r="C40" s="14" t="s">
         <v>18</v>
       </c>
@@ -1515,16 +1508,18 @@
       <c r="F40" s="14"/>
       <c r="G40" s="14"/>
       <c r="H40" s="14"/>
-      <c r="I40" s="20" t="s">
+      <c r="I40" s="14"/>
+      <c r="J40" s="14"/>
+      <c r="K40" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="O40" s="1"/>
-      <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T40" s="1"/>
+      <c r="U40" s="1"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.25">
       <c r="C41" s="12" t="s">
         <v>16</v>
       </c>
@@ -1533,263 +1528,272 @@
       <c r="F41" s="12"/>
       <c r="G41" s="12"/>
       <c r="H41" s="12"/>
-      <c r="I41" s="11" t="s">
+      <c r="I41" s="12"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="N41" s="6"/>
-      <c r="O41" s="1"/>
-      <c r="P41" s="1"/>
+      <c r="P41" s="6"/>
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="M42" s="6"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="1"/>
-      <c r="P42" s="1"/>
+      <c r="T41" s="1"/>
+      <c r="U41" s="1"/>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="O42" s="6"/>
+      <c r="P42" s="6"/>
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="M43" s="6"/>
-      <c r="N43" s="6"/>
-      <c r="O43" s="1"/>
-      <c r="P43" s="1"/>
+      <c r="T42" s="1"/>
+      <c r="U42" s="1"/>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="O43" s="6"/>
+      <c r="P43" s="6"/>
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="M44" s="6"/>
-      <c r="N44" s="6"/>
-      <c r="O44" s="1"/>
-      <c r="P44" s="1"/>
+      <c r="T43" s="1"/>
+      <c r="U43" s="1"/>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="O44" s="6"/>
+      <c r="P44" s="6"/>
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="M45" s="6"/>
-      <c r="N45" s="6"/>
-      <c r="O45" s="1"/>
-      <c r="P45" s="1"/>
+      <c r="T44" s="1"/>
+      <c r="U44" s="1"/>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="O45" s="6"/>
+      <c r="P45" s="6"/>
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="M46" s="6"/>
-      <c r="N46" s="6"/>
-      <c r="O46" s="1"/>
-      <c r="P46" s="1"/>
+      <c r="T45" s="1"/>
+      <c r="U45" s="1"/>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="O46" s="6"/>
+      <c r="P46" s="6"/>
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="M47" s="6"/>
-      <c r="N47" s="6"/>
-      <c r="O47" s="1"/>
-      <c r="P47" s="1"/>
+      <c r="T46" s="1"/>
+      <c r="U46" s="1"/>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="O47" s="6"/>
+      <c r="P47" s="6"/>
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="M48" s="6"/>
-      <c r="N48" s="6"/>
-      <c r="O48" s="1"/>
-      <c r="P48" s="1"/>
+      <c r="T47" s="1"/>
+      <c r="U47" s="1"/>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="O48" s="6"/>
+      <c r="P48" s="6"/>
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
-    </row>
-    <row r="49" spans="13:19" x14ac:dyDescent="0.25">
-      <c r="M49" s="6"/>
-      <c r="N49" s="6"/>
-      <c r="O49" s="1"/>
-      <c r="P49" s="1"/>
+      <c r="T48" s="1"/>
+      <c r="U48" s="1"/>
+    </row>
+    <row r="49" spans="15:21" x14ac:dyDescent="0.25">
+      <c r="O49" s="6"/>
+      <c r="P49" s="6"/>
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
-    </row>
-    <row r="50" spans="13:19" x14ac:dyDescent="0.25">
-      <c r="M50" s="6"/>
-      <c r="N50" s="1"/>
-      <c r="O50" s="1"/>
+      <c r="T49" s="1"/>
+      <c r="U49" s="1"/>
+    </row>
+    <row r="50" spans="15:21" x14ac:dyDescent="0.25">
+      <c r="O50" s="6"/>
       <c r="P50" s="1"/>
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
       <c r="S50" s="1"/>
-    </row>
-    <row r="51" spans="13:19" x14ac:dyDescent="0.25">
-      <c r="M51" s="1"/>
-      <c r="N51" s="1"/>
+      <c r="T50" s="1"/>
+      <c r="U50" s="1"/>
+    </row>
+    <row r="51" spans="15:21" x14ac:dyDescent="0.25">
       <c r="O51" s="1"/>
       <c r="P51" s="1"/>
       <c r="Q51" s="1"/>
       <c r="R51" s="1"/>
       <c r="S51" s="1"/>
-    </row>
-    <row r="52" spans="13:19" x14ac:dyDescent="0.25">
-      <c r="M52" s="1"/>
-      <c r="N52" s="1"/>
+      <c r="T51" s="1"/>
+      <c r="U51" s="1"/>
+    </row>
+    <row r="52" spans="15:21" x14ac:dyDescent="0.25">
       <c r="O52" s="1"/>
       <c r="P52" s="1"/>
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
-    </row>
-    <row r="53" spans="13:19" x14ac:dyDescent="0.25">
-      <c r="M53" s="1"/>
-      <c r="N53" s="1"/>
+      <c r="T52" s="1"/>
+      <c r="U52" s="1"/>
+    </row>
+    <row r="53" spans="15:21" x14ac:dyDescent="0.25">
       <c r="O53" s="1"/>
       <c r="P53" s="1"/>
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
-    </row>
-    <row r="54" spans="13:19" x14ac:dyDescent="0.25">
-      <c r="M54" s="1"/>
-      <c r="N54" s="1"/>
+      <c r="T53" s="1"/>
+      <c r="U53" s="1"/>
+    </row>
+    <row r="54" spans="15:21" x14ac:dyDescent="0.25">
       <c r="O54" s="1"/>
       <c r="P54" s="1"/>
       <c r="Q54" s="1"/>
       <c r="R54" s="1"/>
       <c r="S54" s="1"/>
-    </row>
-    <row r="55" spans="13:19" x14ac:dyDescent="0.25">
-      <c r="M55" s="1"/>
-      <c r="N55" s="1"/>
+      <c r="T54" s="1"/>
+      <c r="U54" s="1"/>
+    </row>
+    <row r="55" spans="15:21" x14ac:dyDescent="0.25">
       <c r="O55" s="1"/>
       <c r="P55" s="1"/>
       <c r="Q55" s="1"/>
       <c r="R55" s="1"/>
       <c r="S55" s="1"/>
-    </row>
-    <row r="56" spans="13:19" x14ac:dyDescent="0.25">
-      <c r="M56" s="1"/>
-      <c r="N56" s="1"/>
+      <c r="T55" s="1"/>
+      <c r="U55" s="1"/>
+    </row>
+    <row r="56" spans="15:21" x14ac:dyDescent="0.25">
       <c r="O56" s="1"/>
       <c r="P56" s="1"/>
       <c r="Q56" s="1"/>
       <c r="R56" s="1"/>
       <c r="S56" s="1"/>
-    </row>
-    <row r="57" spans="13:19" x14ac:dyDescent="0.25">
-      <c r="M57" s="1"/>
-      <c r="N57" s="1"/>
+      <c r="T56" s="1"/>
+      <c r="U56" s="1"/>
+    </row>
+    <row r="57" spans="15:21" x14ac:dyDescent="0.25">
       <c r="O57" s="1"/>
       <c r="P57" s="1"/>
       <c r="Q57" s="1"/>
       <c r="R57" s="1"/>
       <c r="S57" s="1"/>
-    </row>
-    <row r="58" spans="13:19" x14ac:dyDescent="0.25">
-      <c r="M58" s="1"/>
-      <c r="N58" s="1"/>
+      <c r="T57" s="1"/>
+      <c r="U57" s="1"/>
+    </row>
+    <row r="58" spans="15:21" x14ac:dyDescent="0.25">
       <c r="O58" s="1"/>
       <c r="P58" s="1"/>
       <c r="Q58" s="1"/>
       <c r="R58" s="1"/>
       <c r="S58" s="1"/>
-    </row>
-    <row r="59" spans="13:19" x14ac:dyDescent="0.25">
-      <c r="M59" s="1"/>
-      <c r="N59" s="1"/>
+      <c r="T58" s="1"/>
+      <c r="U58" s="1"/>
+    </row>
+    <row r="59" spans="15:21" x14ac:dyDescent="0.25">
       <c r="O59" s="1"/>
       <c r="P59" s="1"/>
       <c r="Q59" s="1"/>
       <c r="R59" s="1"/>
       <c r="S59" s="1"/>
-    </row>
-    <row r="60" spans="13:19" x14ac:dyDescent="0.25">
-      <c r="M60" s="1"/>
-      <c r="N60" s="1"/>
+      <c r="T59" s="1"/>
+      <c r="U59" s="1"/>
+    </row>
+    <row r="60" spans="15:21" x14ac:dyDescent="0.25">
       <c r="O60" s="1"/>
       <c r="P60" s="1"/>
       <c r="Q60" s="1"/>
       <c r="R60" s="1"/>
       <c r="S60" s="1"/>
-    </row>
-    <row r="61" spans="13:19" x14ac:dyDescent="0.25">
-      <c r="M61" s="1"/>
-      <c r="N61" s="1"/>
+      <c r="T60" s="1"/>
+      <c r="U60" s="1"/>
+    </row>
+    <row r="61" spans="15:21" x14ac:dyDescent="0.25">
       <c r="O61" s="1"/>
       <c r="P61" s="1"/>
       <c r="Q61" s="1"/>
       <c r="R61" s="1"/>
       <c r="S61" s="1"/>
-    </row>
-    <row r="62" spans="13:19" x14ac:dyDescent="0.25">
-      <c r="M62" s="1"/>
-      <c r="N62" s="1"/>
+      <c r="T61" s="1"/>
+      <c r="U61" s="1"/>
+    </row>
+    <row r="62" spans="15:21" x14ac:dyDescent="0.25">
       <c r="O62" s="1"/>
       <c r="P62" s="1"/>
       <c r="Q62" s="1"/>
       <c r="R62" s="1"/>
       <c r="S62" s="1"/>
-    </row>
-    <row r="63" spans="13:19" x14ac:dyDescent="0.25">
-      <c r="M63" s="1"/>
-      <c r="N63" s="1"/>
+      <c r="T62" s="1"/>
+      <c r="U62" s="1"/>
+    </row>
+    <row r="63" spans="15:21" x14ac:dyDescent="0.25">
       <c r="O63" s="1"/>
       <c r="P63" s="1"/>
       <c r="Q63" s="1"/>
       <c r="R63" s="1"/>
       <c r="S63" s="1"/>
-    </row>
-    <row r="64" spans="13:19" x14ac:dyDescent="0.25">
-      <c r="M64" s="1"/>
-      <c r="N64" s="1"/>
+      <c r="T63" s="1"/>
+      <c r="U63" s="1"/>
+    </row>
+    <row r="64" spans="15:21" x14ac:dyDescent="0.25">
       <c r="O64" s="1"/>
       <c r="P64" s="1"/>
       <c r="Q64" s="1"/>
       <c r="R64" s="1"/>
       <c r="S64" s="1"/>
-    </row>
-    <row r="65" spans="13:20" x14ac:dyDescent="0.25">
-      <c r="M65" s="1"/>
-      <c r="N65" s="1"/>
+      <c r="T64" s="1"/>
+      <c r="U64" s="1"/>
+    </row>
+    <row r="65" spans="15:22" x14ac:dyDescent="0.25">
       <c r="O65" s="1"/>
       <c r="P65" s="1"/>
       <c r="Q65" s="1"/>
       <c r="R65" s="1"/>
       <c r="S65" s="1"/>
-    </row>
-    <row r="66" spans="13:20" x14ac:dyDescent="0.25">
-      <c r="M66" s="1"/>
-      <c r="N66" s="1"/>
+      <c r="T65" s="1"/>
+      <c r="U65" s="1"/>
+    </row>
+    <row r="66" spans="15:22" x14ac:dyDescent="0.25">
       <c r="O66" s="1"/>
       <c r="P66" s="1"/>
       <c r="Q66" s="1"/>
       <c r="R66" s="1"/>
       <c r="S66" s="1"/>
       <c r="T66" s="1"/>
-    </row>
-    <row r="67" spans="13:20" x14ac:dyDescent="0.25">
-      <c r="M67" s="1"/>
-      <c r="N67" s="1"/>
+      <c r="U66" s="1"/>
+      <c r="V66" s="1"/>
+    </row>
+    <row r="67" spans="15:22" x14ac:dyDescent="0.25">
       <c r="O67" s="1"/>
-    </row>
-    <row r="68" spans="13:20" x14ac:dyDescent="0.25">
-      <c r="M68" s="1"/>
-      <c r="N68" s="1"/>
-    </row>
-    <row r="69" spans="13:20" x14ac:dyDescent="0.25">
-      <c r="M69" s="1"/>
-      <c r="N69" s="1"/>
-    </row>
-    <row r="70" spans="13:20" x14ac:dyDescent="0.25">
-      <c r="M70" s="1"/>
-      <c r="N70" s="1"/>
+      <c r="P67" s="1"/>
+      <c r="Q67" s="1"/>
+    </row>
+    <row r="68" spans="15:22" x14ac:dyDescent="0.25">
+      <c r="O68" s="1"/>
+      <c r="P68" s="1"/>
+    </row>
+    <row r="69" spans="15:22" x14ac:dyDescent="0.25">
+      <c r="O69" s="1"/>
+      <c r="P69" s="1"/>
+    </row>
+    <row r="70" spans="15:22" x14ac:dyDescent="0.25">
+      <c r="O70" s="1"/>
+      <c r="P70" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A5:L5"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
